--- a/LoanOfficer-A/2026/176 bidyabati.xlsx
+++ b/LoanOfficer-A/2026/176 bidyabati.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11800</v>
+        <v>11200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -924,9 +924,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>46172</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -950,9 +956,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>46173</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -976,9 +988,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1002,9 +1020,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46175</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1028,9 +1052,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46176</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1054,9 +1084,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>46177</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>

--- a/LoanOfficer-A/2026/176 bidyabati.xlsx
+++ b/LoanOfficer-A/2026/176 bidyabati.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11200</v>
+        <v>10600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1116,9 +1116,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1142,9 +1148,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>46179</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1168,9 +1180,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>46180</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1194,9 +1212,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>46181</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1220,9 +1244,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>46182</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1246,9 +1276,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>46183</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
